--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
         <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>32216</v>
+        <v>38322</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -583,22 +583,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34992</v>
+        <v>33907</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>44246</v>
+        <v>42971</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -608,16 +608,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -632,11 +632,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>32495</v>
+        <v>34992</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>67680</v>
+        <v>44246</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -662,11 +662,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>33495</v>
+        <v>32495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>52500</v>
+        <v>55870</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -706,16 +706,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -730,28 +730,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="n">
-        <v>31998</v>
+        <v>32495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>56361</v>
+        <v>67680</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sunroof</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -778,10 +791,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33995</v>
+        <v>33495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>69400</v>
+        <v>52500</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -800,7 +813,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -822,35 +835,120 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34992</v>
+        <v>31998</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>63289</v>
+        <v>56361</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>69400</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>34992</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>63289</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>15</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="K10" t="n">
+        <v>16</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -859,6 +957,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4920,7 +5020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5008,39 +5108,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="n">
-        <v>34998</v>
+        <v>32495</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>67017</v>
+        <v>67680</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5053,38 +5157,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="n">
-        <v>34995</v>
+        <v>34998</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>60062</v>
+        <v>67017</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -5102,22 +5202,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>33907</v>
+        <v>34995</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>46771</v>
+        <v>60062</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5126,14 +5226,14 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -5178,7 +5278,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5204,7 +5304,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5212,30 +5312,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>32495</v>
+        <v>27200</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>67680</v>
+        <v>19323</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5248,16 +5348,20 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5265,10 +5369,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>32495</v>
+        <v>34995</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>64792</v>
+        <v>67531</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5277,14 +5381,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -5302,22 +5406,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>27200</v>
+        <v>35299</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19323</v>
+        <v>53475</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5326,19 +5430,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5346,31 +5450,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34995</v>
+        <v>33897</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>67531</v>
+        <v>32954</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5379,19 +5479,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5399,12 +5499,16 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5412,14 +5516,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>35299</v>
+        <v>34995</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>53475</v>
+        <v>60062</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -5428,19 +5532,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5448,48 +5552,48 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>34,795 → 34,995</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>33897</v>
+        <v>32488</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>32954</v>
+        <v>63212</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5497,52 +5601,44 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>34,997 → 33,897</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>34995</v>
+        <v>32999</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>60062</v>
+        <v>55369</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5550,11 +5646,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5567,31 +5659,31 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="n">
-        <v>32488</v>
+        <v>33998</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>63212</v>
+        <v>56937</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5604,39 +5696,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>32999</v>
+        <v>34998</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>55369</v>
+        <v>33650</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5644,23 +5740,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2023</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="n">
-        <v>33998</v>
+        <v>34998</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>56937</v>
+        <v>68226</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
@@ -5669,19 +5773,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5694,38 +5798,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>33650</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5738,16 +5832,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5755,35 +5845,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>34998</v>
+        <v>34990</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>68226</v>
+        <v>48677</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -5793,194 +5883,8 @@
       </c>
       <c r="M17" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Toyotavictoriaville</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>14</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>48677</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>18</v>
-      </c>
-      <c r="I19" t="n">
-        <v>18</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>67531</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>21</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>35098</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>68226</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>AutoTrader</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>21</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M21"/>
+  <autoFilter ref="A1:M17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5998,10 +5902,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30998</v>
+        <v>26500</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>38322</v>
+        <v>37866</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32,995 → 30,998</t>
+          <t>27,500 → 27,200 → 26,500</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33907</v>
+        <v>30998</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>42971</v>
+        <v>38322</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -617,14 +617,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>32,995 → 30,998</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,11 +636,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -644,10 +648,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>34992</v>
+        <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>44246</v>
+        <v>27647</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -657,16 +661,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -681,11 +685,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -693,10 +697,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32495</v>
+        <v>34992</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55870</v>
+        <v>44246</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -706,16 +710,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -764,7 +768,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -779,7 +783,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -787,14 +791,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33495</v>
+        <v>33907</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>52500</v>
+        <v>60831</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -804,16 +808,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof, AWD</t>
+          <t>Sunroof</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -828,28 +832,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>31998</v>
+        <v>33495</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>56361</v>
+        <v>52500</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
@@ -864,41 +881,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="n">
-        <v>33995</v>
+        <v>31998</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>69400</v>
+        <v>56361</v>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -913,42 +917,121 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2023</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="n">
+        <v>33995</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>69400</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sunroof, AWD</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Otogo.ca</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>34992</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>63289</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>16</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="K11" t="n">
+        <v>17</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Lefebvre Toyota</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -959,6 +1042,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5020,7 +5105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5135,7 +5220,7 @@
         <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5180,7 +5265,7 @@
         <v>55</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5229,7 +5314,7 @@
         <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5278,7 +5363,7 @@
         <v>47</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5304,22 +5389,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>27200</v>
+        <v>34995</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19323</v>
+        <v>67531</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
@@ -5328,14 +5413,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5348,16 +5433,12 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>27,500 → 27,200</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5365,14 +5446,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LE S-AWC</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>34995</v>
+        <v>35299</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>67531</v>
+        <v>53475</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -5381,19 +5462,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5406,22 +5487,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>35299</v>
+        <v>33897</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>53475</v>
+        <v>32954</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5430,19 +5511,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5450,27 +5531,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>33897</v>
+        <v>34995</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32954</v>
+        <v>60062</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5479,19 +5564,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5501,45 +5586,41 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>34,997 → 33,897</t>
+          <t>34,795 → 34,995</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>34995</v>
+        <v>32488</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>60062</v>
+        <v>63212</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5552,11 +5633,7 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>34,795 → 34,995</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5569,31 +5646,31 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="n">
-        <v>32488</v>
+        <v>32999</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>63212</v>
+        <v>55369</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5614,26 +5691,26 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>32999</v>
+        <v>33998</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>55369</v>
+        <v>56937</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5651,18 +5728,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="n">
-        <v>33998</v>
+        <v>34998</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>56937</v>
+        <v>33650</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5671,19 +5752,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5691,7 +5772,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5711,7 +5796,7 @@
         <v>34998</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>33650</v>
+        <v>68226</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -5720,14 +5805,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -5740,47 +5825,33 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>35,099 → 35,098 → 34,998</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>34998</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>68226</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Toyotavictoriaville</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5798,33 +5869,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>48677</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -5834,57 +5915,8 @@
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>34990</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>48677</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Otogo.ca, Repentigny Mitsubishi</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>18</v>
-      </c>
-      <c r="I17" t="n">
-        <v>19</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5901,7 +5933,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outlander_phev_search_results.xlsx
+++ b/outlander_phev_search_results.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recently Sold" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Search Results'!$A$1:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lease Takeovers'!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dealers'!$A$1:$G$146</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Recently Sold'!$A$1:$M$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -530,11 +530,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>26500</v>
+        <v>30998</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>37866</v>
+        <v>53754</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>27,500 → 27,200 → 26,500</t>
+          <t>32,995 → 30,998</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SEL</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -591,14 +591,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30998</v>
+        <v>34992</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>38322</v>
+        <v>44246</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -608,27 +608,23 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>32,995 → 30,998</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -651,7 +647,7 @@
         <v>32495</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27647</v>
+        <v>67680</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
@@ -661,16 +657,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Kijiji</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -685,11 +681,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -697,10 +693,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34992</v>
+        <v>33495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>44246</v>
+        <v>52500</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
@@ -715,11 +711,11 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Otogo.ca, Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -734,41 +730,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2023</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="n">
-        <v>32495</v>
+        <v>31998</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>67680</v>
+        <v>56361</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sunroof</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AutoTrader, Kijiji</t>
+          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -783,7 +766,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -791,14 +774,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SEL</t>
+          <t>LE S-AWC</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33907</v>
+        <v>33995</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>60831</v>
+        <v>69400</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
@@ -808,16 +791,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sunroof</t>
+          <t>Sunroof, AWD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -832,206 +815,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2023</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="n">
-        <v>33495</v>
+        <v>34992</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>52500</v>
+        <v>63289</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>31998</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>56361</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Candiac Toyota, Hgregoire Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>33995</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>69400</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Sunroof, AWD</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Otogo.ca</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34992</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>63289</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Blainville Mitsubishi, Stjerome Mitsubishi, Terrebonne Mitsubishi, Vaudreuil Mitsubishi</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>17</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>35,492 → 34,992</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Lefebvre Toyota</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M12"/>
+  <autoFilter ref="A1:M8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -1040,10 +859,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5105,7 +4920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5213,23 +5028,23 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kijiji</t>
+          <t>AutoTrader, Kijiji</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -5242,39 +5057,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>2023</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="n">
-        <v>34998</v>
+        <v>32495</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>67017</v>
+        <v>27647</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hondasoreltracy</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5287,22 +5106,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34995</v>
+        <v>26500</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>60062</v>
+        <v>37866</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -5311,19 +5130,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5331,7 +5150,11 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>27,500 → 27,200 → 26,500</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5348,10 +5171,10 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>31500</v>
+        <v>33907</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>39577</v>
+        <v>60831</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -5360,19 +5183,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5380,52 +5203,38 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LE S-AWC</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>34995</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>67531</v>
-      </c>
+        <v>2023</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Lefebvre Toyota</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5438,43 +5247,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV SE</t>
+          <t>2024 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2024</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="n">
-        <v>35299</v>
+        <v>34998</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>53475</v>
+        <v>67017</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Hondasoreltracy</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -5487,22 +5292,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>33897</v>
+        <v>34995</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32954</v>
+        <v>60062</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
@@ -5511,19 +5316,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -5531,31 +5336,27 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>34,997 → 33,897</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV LE</t>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>SEL</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>34995</v>
+        <v>31500</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>60062</v>
+        <v>39577</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
@@ -5564,19 +5365,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -5586,37 +5387,41 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>34,795 → 34,995</t>
+          <t>35,025 → 35,005 → 33,865 → 33,003 → 30,500 → 32,000 → 31,500</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV LE S-AWC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LE S-AWC</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="n">
-        <v>32488</v>
+        <v>34995</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>63212</v>
+        <v>67531</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Repentigny Mitsubishi</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5625,7 +5430,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5638,39 +5443,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2024 Mitsubishi Outlander PHEV SE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>2024</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="n">
-        <v>32999</v>
+        <v>35299</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>55369</v>
+        <v>53475</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Otogo.ca</t>
+          <t>AutoTrader</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -5683,18 +5492,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV GT</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="n">
-        <v>33998</v>
+        <v>33897</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>56937</v>
+        <v>32954</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
@@ -5703,19 +5516,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -5723,27 +5536,31 @@
           <t>View</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>34,997 → 33,897</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2024 Mitsubishi Outlander PHEV LE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GT S-AWC</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>34998</v>
+        <v>34995</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>33650</v>
+        <v>60062</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -5752,19 +5569,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -5774,50 +5591,46 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>35,099 → 35,098 → 34,998</t>
+          <t>34,795 → 34,995</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2023</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GT S-AWC</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="n">
-        <v>34998</v>
+        <v>32488</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>68226</v>
+        <v>63212</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>AutoTrader</t>
+          <t>Repentigny Mitsubishi</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -5830,33 +5643,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024 Mitsubishi Outlander PHEV</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>32999</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>55369</v>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Toyotavictoriaville</t>
+          <t>Otogo.ca</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -5869,54 +5688,240 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+          <t>2023 Mitsubishi Outlander PHEV</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2023</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SEL</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>34990</v>
+        <v>33998</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>48677</v>
+        <v>56937</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>33650</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>35,099 → 35,098 → 34,998</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV GT S-AWC</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GT S-AWC</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>34998</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>68226</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AutoTrader</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>17</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024 Mitsubishi Outlander PHEV</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Toyotavictoriaville</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>17</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2023 Mitsubishi Outlander PHEV SEL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SEL</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>48677</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Otogo.ca, Repentigny Mitsubishi</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="H20" t="n">
         <v>18</v>
       </c>
-      <c r="I16" t="n">
-        <v>20</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="I20" t="n">
+        <v>21</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M20"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -5933,6 +5938,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
